--- a/stories/arbres/TREE-COL-018.xlsx
+++ b/stories/arbres/TREE-COL-018.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ninon arrive à l'école avec maman. La maîtresse parle. Ninon aime écouter. Maman dit : tu écoutes. Si tu as un malaise, tu viens raconter à la maison.</t>
+          <t>Ninon arrive à l'école avec maman. La maîtresse parle. Ninon aime écouter. Tu écoutes. Si tu as un malaise, tu viens raconter à la maison.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,12 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Ninon arrive à l'école avec maman. La maîtresse parle. Ninon aime écouter.
+maman|Tu écoutes. Si tu as un malaise, tu viens raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1510,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le tapis, la table, ou le préau.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1645,6 +1673,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sur le tapis, Ninon écoute. Un chuchotement. Un malaise. Le soir, elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1821,6 +1854,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Sur le tapis, Ninon a un malaise. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1989,6 +2027,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Ninon a écouté. Si malaise, elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2222,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre l'histoire, le dessin, ou la chanson.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2337,6 +2385,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire. Ninon écoute. Malaise. Elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2523,6 +2576,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2681,6 +2739,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Ninon rejoint maman. Elle a écouté à le tapis, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2843,6 +2906,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3001,6 +3069,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Ninon rejoint papa. Elle a écouté à le tapis, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3163,6 +3236,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3321,6 +3399,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Ninon rejoint la sœur. Elle a écouté à le tapis, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3483,6 +3566,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3645,6 +3733,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Le dessin. Ninon écoute. Malaise. Raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3831,6 +3924,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3993,6 +4091,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Ninon rejoint maman. Elle a écouté à le tapis, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4155,6 +4258,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4317,6 +4425,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Ninon rejoint papa. Elle a écouté à le tapis, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4479,6 +4592,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4641,6 +4759,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Ninon rejoint la sœur. Elle a écouté à le tapis, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4803,6 +4926,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4961,6 +5089,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|La chanson. Ninon écoute. Malaise. Elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5147,6 +5280,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5305,6 +5443,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Ninon rejoint maman. Elle a écouté à le tapis, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5467,6 +5610,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5625,6 +5773,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Ninon rejoint papa. Elle a écouté à le tapis, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5787,6 +5940,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5945,6 +6103,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Ninon rejoint la sœur. Elle a écouté à le tapis, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6107,6 +6270,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6265,6 +6433,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|À la table, Ninon écoute. Un mot la gêne. Malaise. Elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6441,6 +6614,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|À la table, Ninon a un malaise. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -6609,6 +6787,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Écouter. Si malaise, raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6799,6 +6982,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre l'histoire, le dessin, ou la chanson.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6961,6 +7149,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|À la table, l'histoire. Ninon écoute. Malaise. Raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7147,6 +7340,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7305,6 +7503,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Ninon rejoint maman. Elle a écouté à la table, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7467,6 +7670,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7625,6 +7833,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Ninon rejoint papa. Elle a écouté à la table, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7787,6 +8000,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7945,6 +8163,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Ninon rejoint la sœur. Elle a écouté à la table, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8107,6 +8330,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8269,6 +8497,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Le dessin à la table. Ninon écoute. Malaise. Elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8455,6 +8688,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8617,6 +8855,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Ninon rejoint maman. Elle a écouté à la table, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8779,6 +9022,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8941,6 +9189,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Ninon rejoint papa. Elle a écouté à la table, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9103,6 +9356,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9265,6 +9523,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Ninon rejoint la sœur. Elle a écouté à la table, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9427,6 +9690,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9589,6 +9857,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|La chanson à la table. Ninon écoute. Malaise. Raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9775,6 +10048,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9933,6 +10211,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Ninon rejoint maman. Elle a écouté à la table, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10095,6 +10378,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10253,6 +10541,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Ninon rejoint papa. Elle a écouté à la table, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10415,6 +10708,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10573,6 +10871,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Ninon rejoint la sœur. Elle a écouté à la table, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10735,6 +11038,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10897,6 +11205,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Au préau, Ninon écoute. Son ventre se serre. Malaise. Elle racontera à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11073,6 +11386,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Au préau, Ninon a un malaise. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -11241,6 +11559,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Ninon a su écouter. Elle saura raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11431,6 +11754,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre l'histoire, le dessin, ou la chanson.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11589,6 +11917,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Au préau, l'histoire. Ninon écoute. Malaise. Elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11775,6 +12108,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11933,6 +12271,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Ninon rejoint maman. Elle a écouté à le préau, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12095,6 +12438,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12253,6 +12601,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Ninon rejoint papa. Elle a écouté à le préau, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12415,6 +12768,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12573,6 +12931,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Ninon rejoint la sœur. Elle a écouté à le préau, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12735,6 +13098,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12897,6 +13265,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Le dessin au préau. Ninon écoute. Malaise. Raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13083,6 +13456,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13245,6 +13623,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Ninon rejoint maman. Elle a écouté à le préau, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13407,6 +13790,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13569,6 +13957,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Ninon rejoint papa. Elle a écouté à le préau, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13731,6 +14124,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13893,6 +14291,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Ninon rejoint la sœur. Elle a écouté à le préau, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14055,6 +14458,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14213,6 +14621,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|La chanson au préau. Ninon écoute. Malaise. Elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14399,6 +14812,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14557,6 +14975,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Ninon rejoint maman. Elle a écouté à le préau, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14719,6 +15142,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14877,6 +15305,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Ninon rejoint papa. Elle a écouté à le préau, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15039,6 +15472,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15197,6 +15635,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Ninon rejoint la sœur. Elle a écouté à le préau, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15359,6 +15802,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15377,7 +15825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15394,6 +15842,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-018.xlsx
+++ b/stories/arbres/TREE-COL-018.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1324,6 +1329,7 @@
 maman|Tu écoutes. Si tu as un malaise, tu viens raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1515,6 +1521,7 @@
           <t>narrateur|On peut prendre le tapis, la table, ou le préau.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1678,6 +1685,7 @@
           <t>narrateur|Sur le tapis, Ninon écoute. Un chuchotement. Un malaise. Le soir, elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1861,6 +1869,7 @@
           <t>narrateur|Sur le tapis, Ninon a un malaise. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2032,6 +2041,7 @@
           <t>narrateur|Ninon a écouté. Si malaise, elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2227,6 +2237,7 @@
           <t>narrateur|On peut prendre l'histoire, le dessin, ou la chanson.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2390,6 +2401,7 @@
           <t>narrateur|L'histoire. Ninon écoute. Malaise. Elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2581,6 +2593,7 @@
           <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2744,6 +2757,7 @@
           <t>narrateur|Le soir, Ninon rejoint maman. Elle a écouté à le tapis, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2911,6 +2925,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3074,6 +3089,7 @@
           <t>narrateur|Le soir, Ninon rejoint papa. Elle a écouté à le tapis, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3241,6 +3257,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3404,6 +3421,7 @@
           <t>narrateur|Le soir, Ninon rejoint la sœur. Elle a écouté à le tapis, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3571,6 +3589,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3738,6 +3757,7 @@
           <t>narrateur|Le dessin. Ninon écoute. Malaise. Raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3929,6 +3949,7 @@
           <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4096,6 +4117,7 @@
           <t>narrateur|Le soir, Ninon rejoint maman. Elle a écouté à le tapis, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4263,6 +4285,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4430,6 +4453,7 @@
           <t>narrateur|Le soir, Ninon rejoint papa. Elle a écouté à le tapis, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4597,6 +4621,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4764,6 +4789,7 @@
           <t>narrateur|Le soir, Ninon rejoint la sœur. Elle a écouté à le tapis, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4931,6 +4957,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5094,6 +5121,7 @@
           <t>narrateur|La chanson. Ninon écoute. Malaise. Elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5285,6 +5313,7 @@
           <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5448,6 +5477,7 @@
           <t>narrateur|Le soir, Ninon rejoint maman. Elle a écouté à le tapis, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5615,6 +5645,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5778,6 +5809,7 @@
           <t>narrateur|Le soir, Ninon rejoint papa. Elle a écouté à le tapis, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5945,6 +5977,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6108,6 +6141,7 @@
           <t>narrateur|Le soir, Ninon rejoint la sœur. Elle a écouté à le tapis, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6275,6 +6309,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6438,6 +6473,7 @@
           <t>narrateur|À la table, Ninon écoute. Un mot la gêne. Malaise. Elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6621,6 +6657,7 @@
           <t>narrateur|À la table, Ninon a un malaise. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6792,6 +6829,7 @@
           <t>narrateur|Oui. Écouter. Si malaise, raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6987,6 +7025,7 @@
           <t>narrateur|On peut prendre l'histoire, le dessin, ou la chanson.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7154,6 +7193,7 @@
           <t>narrateur|À la table, l'histoire. Ninon écoute. Malaise. Raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7345,6 +7385,7 @@
           <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7508,6 +7549,7 @@
           <t>narrateur|Le soir, Ninon rejoint maman. Elle a écouté à la table, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7675,6 +7717,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7838,6 +7881,7 @@
           <t>narrateur|Le soir, Ninon rejoint papa. Elle a écouté à la table, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8005,6 +8049,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8168,6 +8213,7 @@
           <t>narrateur|Le soir, Ninon rejoint la sœur. Elle a écouté à la table, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8335,6 +8381,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8502,6 +8549,7 @@
           <t>narrateur|Le dessin à la table. Ninon écoute. Malaise. Elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8693,6 +8741,7 @@
           <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8860,6 +8909,7 @@
           <t>narrateur|Le soir, Ninon rejoint maman. Elle a écouté à la table, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9027,6 +9077,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9194,6 +9245,7 @@
           <t>narrateur|Le soir, Ninon rejoint papa. Elle a écouté à la table, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9361,6 +9413,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9528,6 +9581,7 @@
           <t>narrateur|Le soir, Ninon rejoint la sœur. Elle a écouté à la table, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9695,6 +9749,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9862,6 +9917,7 @@
           <t>narrateur|La chanson à la table. Ninon écoute. Malaise. Raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10053,6 +10109,7 @@
           <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10216,6 +10273,7 @@
           <t>narrateur|Le soir, Ninon rejoint maman. Elle a écouté à la table, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10383,6 +10441,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10546,6 +10605,7 @@
           <t>narrateur|Le soir, Ninon rejoint papa. Elle a écouté à la table, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10713,6 +10773,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10876,6 +10937,7 @@
           <t>narrateur|Le soir, Ninon rejoint la sœur. Elle a écouté à la table, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11043,6 +11105,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11210,6 +11273,7 @@
           <t>narrateur|Au préau, Ninon écoute. Son ventre se serre. Malaise. Elle racontera à la maison.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11393,6 +11457,7 @@
           <t>narrateur|Au préau, Ninon a un malaise. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11564,6 +11629,7 @@
           <t>narrateur|Ninon a su écouter. Elle saura raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11759,6 +11825,7 @@
           <t>narrateur|On peut prendre l'histoire, le dessin, ou la chanson.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11922,6 +11989,7 @@
           <t>narrateur|Au préau, l'histoire. Ninon écoute. Malaise. Elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12113,6 +12181,7 @@
           <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12276,6 +12345,7 @@
           <t>narrateur|Le soir, Ninon rejoint maman. Elle a écouté à le préau, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12443,6 +12513,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12606,6 +12677,7 @@
           <t>narrateur|Le soir, Ninon rejoint papa. Elle a écouté à le préau, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12773,6 +12845,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12936,6 +13009,7 @@
           <t>narrateur|Le soir, Ninon rejoint la sœur. Elle a écouté à le préau, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13103,6 +13177,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13270,6 +13345,7 @@
           <t>narrateur|Le dessin au préau. Ninon écoute. Malaise. Raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13461,6 +13537,7 @@
           <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13628,6 +13705,7 @@
           <t>narrateur|Le soir, Ninon rejoint maman. Elle a écouté à le préau, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13795,6 +13873,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13962,6 +14041,7 @@
           <t>narrateur|Le soir, Ninon rejoint papa. Elle a écouté à le préau, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14129,6 +14209,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14296,6 +14377,7 @@
           <t>narrateur|Le soir, Ninon rejoint la sœur. Elle a écouté à le préau, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14463,6 +14545,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14626,6 +14709,7 @@
           <t>narrateur|La chanson au préau. Ninon écoute. Malaise. Elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14817,6 +14901,7 @@
           <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14980,6 +15065,7 @@
           <t>narrateur|Le soir, Ninon rejoint maman. Elle a écouté à le préau, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15147,6 +15233,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15310,6 +15397,7 @@
           <t>narrateur|Le soir, Ninon rejoint papa. Elle a écouté à le préau, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15477,6 +15565,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15640,6 +15729,7 @@
           <t>narrateur|Le soir, Ninon rejoint la sœur. Elle a écouté à le préau, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15807,6 +15897,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15825,7 +15916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15849,6 +15940,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15863,7 +15968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16050,6 +16155,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-COL-018.xlsx
+++ b/stories/arbres/TREE-COL-018.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ninon écoute, puis raconte à la maison</t>
+          <t>Le rond de soleil sur le tapis</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un rond de soleil dort sur le tapis. Nina écoute la maîtresse. Un chuchotement serre son ventre. Le soir, elle raconte à papa et maman.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ninon arrive à l'école avec maman. La maîtresse parle. Ninon aime écouter. Tu écoutes. Si tu as un malaise, tu viens raconter à la maison.</t>
+          <t>Les patères font une rangée de bois. Le manteau bleu de Nina est encore tiède. Ça sent la colle d'hier, tout doux. La fenêtre est un peu embuée. Un rond de soleil dort sur le tapis. Maman a serré la main de Nina, près de la porte. Bonne journée, Nina. Tu écoutes la maîtresse. Si tu as un malaise, tu viens raconter à la maison. D'accord. En ce moment, la maîtresse tapote la table. Un petit toc, tout net. On s'assoit. On écoute. Nina aime écouter. Le tapis, la table, le préau attendent. Un camarade se penche déjà, tout près. Nina sent son ventre, tout calme encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,11 +1337,31 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Ninon arrive à l'école avec maman. La maîtresse parle. Ninon aime écouter.
-maman|Tu écoutes. Si tu as un malaise, tu viens raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Les patères font une rangée de bois.
+narrateur|Le manteau bleu de Nina est encore tiède.
+narrateur|Ça sent la colle d'hier, tout doux.
+narrateur|La fenêtre est un peu embuée.
+narrateur|Un rond de soleil dort sur le tapis.
+narrateur|Maman a serré la main de Nina, près de la porte.
+maman|Bonne journée, Nina.
+maman|Tu écoutes la maîtresse.
+papa|Si tu as un malaise, tu viens raconter à la maison.
+enfant-f|D'accord.
+narrateur|En ce moment, la maîtresse tapote la table.
+narrateur|Un petit toc, tout net.
+maitresse|On s'assoit.
+maitresse|On écoute.
+narrateur|Nina aime écouter.
+narrateur|Le tapis, la table, le préau attendent.
+narrateur|Un camarade se penche déjà, tout près.
+narrateur|Nina sent son ventre, tout calme encore.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>porte</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1354,7 +1386,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le tapis, la table, ou le préau.</t>
+          <t>On peut s'asseoir à trois endroits. Le tapis, la table, ou le préau ? Tu écoutes. Si malaise, tu racontes à la maison.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1518,7 +1550,10 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le tapis, la table, ou le préau.</t>
+          <t>narrateur|On peut s'asseoir à trois endroits.
+maitresse|Le tapis, la table, ou le préau ?
+maman|Tu écoutes.
+papa|Si malaise, tu racontes à la maison.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1546,7 +1581,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sur le tapis, Ninon écoute. Un chuchotement. Un malaise. Le soir, elle raconte à la maison.</t>
+          <t>Nina s'assoit sur le tapis. La laine est chaude, sous les genoux. Le rond de soleil a bougé, un peu. On écoute, sur le tapis. Nina écoute. Un camarade se penche. Il chuchote, tout près. Nina sent un malaise. Son ventre se serre, tout petit. Elle reste sur le tapis. Elle écoute encore la maîtresse. Ce soir, je raconte. Tu écoutes. Si malaise, tu racontes à la maison. Merci, Nina. Tu as écouté. Le tapis chatouille encore un genou.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1682,7 +1717,23 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sur le tapis, Ninon écoute. Un chuchotement. Un malaise. Le soir, elle raconte à la maison.</t>
+          <t>narrateur|Nina s'assoit sur le tapis.
+narrateur|La laine est chaude, sous les genoux.
+narrateur|Le rond de soleil a bougé, un peu.
+maitresse|On écoute, sur le tapis.
+narrateur|Nina écoute.
+narrateur|Un camarade se penche.
+narrateur|Il chuchote, tout près.
+narrateur|Nina sent un malaise.
+narrateur|Son ventre se serre, tout petit.
+narrateur|Elle reste sur le tapis.
+narrateur|Elle écoute encore la maîtresse.
+enfant-f|Ce soir, je raconte.
+maman|Tu écoutes.
+maman|Si malaise, tu racontes à la maison.
+maitresse|Merci, Nina.
+maitresse|Tu as écouté.
+narrateur|Le tapis chatouille encore un genou.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1710,7 +1761,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Sur le tapis, Ninon a un malaise. Que fait-elle ?</t>
+          <t>Sur le tapis, Nina a un malaise. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1866,7 +1917,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Sur le tapis, Ninon a un malaise. Que fait-elle ?</t>
+          <t>narrateur|Sur le tapis, Nina a un malaise.
+maman|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1894,7 +1946,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Ninon a écouté. Si malaise, elle raconte à la maison.</t>
+          <t>Oui. Elle raconte à la maison. Nina souffle un peu. Le rond de soleil a encore bougé. J'écoute. Puis je raconte. Bravo, Nina. C'est du bon travail. La laine du tapis redevient douce.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2038,7 +2090,15 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Ninon a écouté. Si malaise, elle raconte à la maison.</t>
+          <t>maman|Oui.
+maman|Elle raconte à la maison.
+narrateur|Nina souffle un peu.
+narrateur|Le rond de soleil a encore bougé.
+enfant-f|J'écoute.
+enfant-f|Puis je raconte.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+narrateur|La laine du tapis redevient douce.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2066,7 +2126,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre l'histoire, le dessin, ou la chanson.</t>
+          <t>Trois choses encore, dans la classe. L'histoire, le dessin, ou la chanson ? On écoute. Ensuite, si malaise, on raconte à la maison.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2234,7 +2294,10 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre l'histoire, le dessin, ou la chanson.</t>
+          <t>narrateur|Trois choses encore, dans la classe.
+maitresse|L'histoire, le dessin, ou la chanson ?
+maman|On écoute.
+papa|Ensuite, si malaise, on raconte à la maison.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2262,7 +2325,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>L'histoire. Ninon écoute. Malaise. Elle raconte à la maison.</t>
+          <t>La maîtresse ouvre le livre. Il y a un renard, tout roux. Une page sent encore l'encre. On écoute l'histoire. Nina écoute. Le malaise est encore là, tout petit. Elle reste sage. Elle écoute jusqu'au bout. Je raconte à la maison. Oui. On t'écoute. Le renard du livre est assis, comme sur le tapis. Nina garde le tapis dans sa tête. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2398,7 +2461,21 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire. Ninon écoute. Malaise. Elle raconte à la maison.</t>
+          <t>narrateur|La maîtresse ouvre le livre.
+narrateur|Il y a un renard, tout roux.
+narrateur|Une page sent encore l'encre.
+maitresse|On écoute l'histoire.
+narrateur|Nina écoute.
+narrateur|Le malaise est encore là, tout petit.
+narrateur|Elle reste sage.
+narrateur|Elle écoute jusqu'au bout.
+enfant-f|Je raconte à la maison.
+maman|Oui.
+maman|On t'écoute.
+narrateur|Le renard du livre est assis, comme sur le tapis.
+narrateur|Nina garde le tapis dans sa tête.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr"/>
@@ -2426,7 +2503,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre maman, papa, ou la sœur.</t>
+          <t>Le soir, à la maison, trois chemins. Maman, papa, ou le doudou ? On t'écoute.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2590,7 +2667,9 @@
       <c r="AV9" s="2" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+          <t>narrateur|Le soir, à la maison, trois chemins.
+maman|Maman, papa, ou le doudou ?
+papa|On t'écoute.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2618,7 +2697,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Ninon rejoint maman. Elle a écouté à le tapis, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
+          <t>Le soir, la cuisine sent la soupe. La louche fait un petit bruit, contre la casserole. Nina rejoint maman. Te voilà, Nina. Tu as faim ? Un peu. Nina revoit le renard du livre, près de la soupe. Nina se souvient de le tapis. Elle se souvient de l'histoire. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2754,7 +2833,28 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Ninon rejoint maman. Elle a écouté à le tapis, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
+          <t>narrateur|Le soir, la cuisine sent la soupe.
+narrateur|La louche fait un petit bruit, contre la casserole.
+narrateur|Nina rejoint maman.
+maman|Te voilà, Nina.
+maman|Tu as faim ?
+enfant-f|Un peu.
+narrateur|Nina revoit le renard du livre, près de la soupe.
+narrateur|Nina se souvient de le tapis.
+narrateur|Elle se souvient de l'histoire.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr"/>
@@ -2782,7 +2882,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a écouté sur le tapis. Elle a vécu l'histoire. Le soir, elle a rejoint maman. La soupe fume encore, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2922,7 +3022,15 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a écouté sur le tapis.
+narrateur|Elle a vécu l'histoire.
+narrateur|Le soir, elle a rejoint maman.
+narrateur|La soupe fume encore, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2950,7 +3058,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Ninon rejoint papa. Elle a écouté à le tapis, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
+          <t>Le soir, la lampe fait un rond jaune. Papa est dans le fauteuil. Nina rejoint papa. Viens. On a le temps. J'ai quelque chose. Nina revoit le tapis, dans le rond de la lampe. Nina se souvient de le tapis. Elle se souvient de l'histoire. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3086,7 +3194,28 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Ninon rejoint papa. Elle a écouté à le tapis, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
+          <t>narrateur|Le soir, la lampe fait un rond jaune.
+narrateur|Papa est dans le fauteuil.
+narrateur|Nina rejoint papa.
+papa|Viens.
+papa|On a le temps.
+enfant-f|J'ai quelque chose.
+narrateur|Nina revoit le tapis, dans le rond de la lampe.
+narrateur|Nina se souvient de le tapis.
+narrateur|Elle se souvient de l'histoire.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3114,7 +3243,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a écouté sur le tapis. Elle a vécu l'histoire. Le soir, elle a rejoint papa. La lampe reste allumée, un moment. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3254,7 +3383,15 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a écouté sur le tapis.
+narrateur|Elle a vécu l'histoire.
+narrateur|Le soir, elle a rejoint papa.
+narrateur|La lampe reste allumée, un moment.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3282,7 +3419,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Ninon rejoint la sœur. Elle a écouté à le tapis, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
+          <t>Le soir, le doudou attend sur le lit. Il est tiède, un peu froissé. Nina le serre. Toi d'abord. Puis elle va vers papa et maman. On t'écoute. Le doudou a l'air d'écouter l'histoire, lui aussi. Nina se souvient de le tapis. Elle se souvient de l'histoire. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3418,7 +3555,28 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Ninon rejoint la sœur. Elle a écouté à le tapis, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
+          <t>narrateur|Le soir, le doudou attend sur le lit.
+narrateur|Il est tiède, un peu froissé.
+narrateur|Nina le serre.
+enfant-f|Toi d'abord.
+narrateur|Puis elle va vers papa et maman.
+maman|On t'écoute.
+narrateur|Le doudou a l'air d'écouter l'histoire, lui aussi.
+narrateur|Nina se souvient de le tapis.
+narrateur|Elle se souvient de l'histoire.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr"/>
@@ -3446,7 +3604,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a écouté sur le tapis. Elle a vécu l'histoire. Le soir, elle a rejoint le doudou. Le doudou s'endort contre l'épaule. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3586,7 +3744,15 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a écouté sur le tapis.
+narrateur|Elle a vécu l'histoire.
+narrateur|Le soir, elle a rejoint le doudou.
+narrateur|Le doudou s'endort contre l'épaule.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3614,7 +3780,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Le dessin. Ninon écoute. Malaise. Raconter à la maison.</t>
+          <t>Nina prend le crayon jaune. Le bois est lisse, un peu chaud. Elle dessine un rond, comme le soleil. On écoute, pendant le dessin. Nina écoute. Le malaise serre encore un peu. Elle pose le crayon, tout droit. Ce soir, je raconte. Tu as écouté. Ensuite, tu racontes. Le rond jaune brille sur le papier. Le rond jaune ressemble au soleil du tapis. Nina garde le tapis dans sa tête. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3754,7 +3920,21 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Le dessin. Ninon écoute. Malaise. Raconter à la maison.</t>
+          <t>narrateur|Nina prend le crayon jaune.
+narrateur|Le bois est lisse, un peu chaud.
+narrateur|Elle dessine un rond, comme le soleil.
+maitresse|On écoute, pendant le dessin.
+narrateur|Nina écoute.
+narrateur|Le malaise serre encore un peu.
+narrateur|Elle pose le crayon, tout droit.
+enfant-f|Ce soir, je raconte.
+papa|Tu as écouté.
+papa|Ensuite, tu racontes.
+narrateur|Le rond jaune brille sur le papier.
+narrateur|Le rond jaune ressemble au soleil du tapis.
+narrateur|Nina garde le tapis dans sa tête.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr"/>
@@ -3782,7 +3962,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre maman, papa, ou la sœur.</t>
+          <t>Le soir, à la maison, trois chemins. Maman, papa, ou le doudou ? On t'écoute.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3946,7 +4126,9 @@
       <c r="AV17" s="2" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+          <t>narrateur|Le soir, à la maison, trois chemins.
+maman|Maman, papa, ou le doudou ?
+papa|On t'écoute.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -3974,7 +4156,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Ninon rejoint maman. Elle a écouté à le tapis, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
+          <t>Le soir, la cuisine sent la soupe. La louche fait un petit bruit, contre la casserole. Nina rejoint maman. Te voilà, Nina. Tu as faim ? Un peu. Le rond jaune est encore dans sa tête, près de la soupe. Nina se souvient de le tapis. Elle se souvient de le dessin. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4114,7 +4296,28 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Ninon rejoint maman. Elle a écouté à le tapis, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
+          <t>narrateur|Le soir, la cuisine sent la soupe.
+narrateur|La louche fait un petit bruit, contre la casserole.
+narrateur|Nina rejoint maman.
+maman|Te voilà, Nina.
+maman|Tu as faim ?
+enfant-f|Un peu.
+narrateur|Le rond jaune est encore dans sa tête, près de la soupe.
+narrateur|Nina se souvient de le tapis.
+narrateur|Elle se souvient de le dessin.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr"/>
@@ -4142,7 +4345,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a écouté sur le tapis. Elle a vécu le dessin. Le soir, elle a rejoint maman. La soupe fume encore, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4282,7 +4485,15 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a écouté sur le tapis.
+narrateur|Elle a vécu le dessin.
+narrateur|Le soir, elle a rejoint maman.
+narrateur|La soupe fume encore, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4310,7 +4521,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Ninon rejoint papa. Elle a écouté à le tapis, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
+          <t>Le soir, la lampe fait un rond jaune. Papa est dans le fauteuil. Nina rejoint papa. Viens. On a le temps. J'ai quelque chose. Nina a un peu de jaune au doigt, sous la lampe. Nina se souvient de le tapis. Elle se souvient de le dessin. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4450,7 +4661,28 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Ninon rejoint papa. Elle a écouté à le tapis, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
+          <t>narrateur|Le soir, la lampe fait un rond jaune.
+narrateur|Papa est dans le fauteuil.
+narrateur|Nina rejoint papa.
+papa|Viens.
+papa|On a le temps.
+enfant-f|J'ai quelque chose.
+narrateur|Nina a un peu de jaune au doigt, sous la lampe.
+narrateur|Nina se souvient de le tapis.
+narrateur|Elle se souvient de le dessin.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4478,7 +4710,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a écouté sur le tapis. Elle a vécu le dessin. Le soir, elle a rejoint papa. La lampe reste allumée, un moment. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4618,7 +4850,15 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a écouté sur le tapis.
+narrateur|Elle a vécu le dessin.
+narrateur|Le soir, elle a rejoint papa.
+narrateur|La lampe reste allumée, un moment.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4646,7 +4886,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Ninon rejoint la sœur. Elle a écouté à le tapis, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
+          <t>Le soir, le doudou attend sur le lit. Il est tiède, un peu froissé. Nina le serre. Toi d'abord. Puis elle va vers papa et maman. On t'écoute. Le doudou a un trait jaune, tout petit, sur l'oreille. Nina se souvient de le tapis. Elle se souvient de le dessin. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4786,7 +5026,28 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Ninon rejoint la sœur. Elle a écouté à le tapis, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
+          <t>narrateur|Le soir, le doudou attend sur le lit.
+narrateur|Il est tiède, un peu froissé.
+narrateur|Nina le serre.
+enfant-f|Toi d'abord.
+narrateur|Puis elle va vers papa et maman.
+maman|On t'écoute.
+narrateur|Le doudou a un trait jaune, tout petit, sur l'oreille.
+narrateur|Nina se souvient de le tapis.
+narrateur|Elle se souvient de le dessin.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr"/>
@@ -4814,7 +5075,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a écouté sur le tapis. Elle a vécu le dessin. Le soir, elle a rejoint le doudou. Le doudou s'endort contre l'épaule. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4954,7 +5215,15 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a écouté sur le tapis.
+narrateur|Elle a vécu le dessin.
+narrateur|Le soir, elle a rejoint le doudou.
+narrateur|Le doudou s'endort contre l'épaule.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -4982,7 +5251,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>La chanson. Ninon écoute. Malaise. Elle raconte à la maison.</t>
+          <t>La maîtresse tape deux fois dans les mains. La chanson est douce, tout simple. On écoute la chanson. Nina écoute. Elle ne chuchote pas. Le malaise reste, tout petit. Je raconte à maman. Ou à papa. Oui. Si malaise, tu racontes à la maison. Les mains de Nina se posent sur ses genoux. La chanson fait un peu danser la laine. Nina garde le tapis dans sa tête. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5118,10 +5387,28 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|La chanson. Ninon écoute. Malaise. Elle raconte à la maison.</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr"/>
+          <t>narrateur|La maîtresse tape deux fois dans les mains.
+narrateur|La chanson est douce, tout simple.
+maitresse|On écoute la chanson.
+narrateur|Nina écoute.
+narrateur|Elle ne chuchote pas.
+narrateur|Le malaise reste, tout petit.
+enfant-f|Je raconte à maman.
+enfant-f|Ou à papa.
+maman|Oui.
+maman|Si malaise, tu racontes à la maison.
+narrateur|Les mains de Nina se posent sur ses genoux.
+narrateur|La chanson fait un peu danser la laine.
+narrateur|Nina garde le tapis dans sa tête.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>chanson</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5146,7 +5433,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre maman, papa, ou la sœur.</t>
+          <t>Le soir, à la maison, trois chemins. Maman, papa, ou le doudou ? On t'écoute.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5310,7 +5597,9 @@
       <c r="AV25" s="2" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+          <t>narrateur|Le soir, à la maison, trois chemins.
+maman|Maman, papa, ou le doudou ?
+papa|On t'écoute.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5338,7 +5627,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Ninon rejoint maman. Elle a écouté à le tapis, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
+          <t>Le soir, la cuisine sent la soupe. La louche fait un petit bruit, contre la casserole. Nina rejoint maman. Te voilà, Nina. Tu as faim ? Un peu. Nina chante un mot, tout bas, près de maman. Nina se souvient de le tapis. Elle se souvient de la chanson. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5474,7 +5763,28 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Ninon rejoint maman. Elle a écouté à le tapis, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
+          <t>narrateur|Le soir, la cuisine sent la soupe.
+narrateur|La louche fait un petit bruit, contre la casserole.
+narrateur|Nina rejoint maman.
+maman|Te voilà, Nina.
+maman|Tu as faim ?
+enfant-f|Un peu.
+narrateur|Nina chante un mot, tout bas, près de maman.
+narrateur|Nina se souvient de le tapis.
+narrateur|Elle se souvient de la chanson.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr"/>
@@ -5502,7 +5812,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a écouté sur le tapis. Elle a vécu la chanson. Le soir, elle a rejoint maman. La soupe fume encore, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5642,7 +5952,15 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a écouté sur le tapis.
+narrateur|Elle a vécu la chanson.
+narrateur|Le soir, elle a rejoint maman.
+narrateur|La soupe fume encore, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5670,7 +5988,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Ninon rejoint papa. Elle a écouté à le tapis, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
+          <t>Le soir, la lampe fait un rond jaune. Papa est dans le fauteuil. Nina rejoint papa. Viens. On a le temps. J'ai quelque chose. Papa reconnaît la chanson, tout doux. Nina se souvient de le tapis. Elle se souvient de la chanson. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5806,7 +6124,28 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Ninon rejoint papa. Elle a écouté à le tapis, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
+          <t>narrateur|Le soir, la lampe fait un rond jaune.
+narrateur|Papa est dans le fauteuil.
+narrateur|Nina rejoint papa.
+papa|Viens.
+papa|On a le temps.
+enfant-f|J'ai quelque chose.
+narrateur|Papa reconnaît la chanson, tout doux.
+narrateur|Nina se souvient de le tapis.
+narrateur|Elle se souvient de la chanson.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5834,7 +6173,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a écouté sur le tapis. Elle a vécu la chanson. Le soir, elle a rejoint papa. La lampe reste allumée, un moment. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -5974,7 +6313,15 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a écouté sur le tapis.
+narrateur|Elle a vécu la chanson.
+narrateur|Le soir, elle a rejoint papa.
+narrateur|La lampe reste allumée, un moment.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6002,7 +6349,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Ninon rejoint la sœur. Elle a écouté à le tapis, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
+          <t>Le soir, le doudou attend sur le lit. Il est tiède, un peu froissé. Nina le serre. Toi d'abord. Puis elle va vers papa et maman. On t'écoute. Le doudou balance un peu, comme la chanson. Nina se souvient de le tapis. Elle se souvient de la chanson. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6138,7 +6485,28 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Ninon rejoint la sœur. Elle a écouté à le tapis, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
+          <t>narrateur|Le soir, le doudou attend sur le lit.
+narrateur|Il est tiède, un peu froissé.
+narrateur|Nina le serre.
+enfant-f|Toi d'abord.
+narrateur|Puis elle va vers papa et maman.
+maman|On t'écoute.
+narrateur|Le doudou balance un peu, comme la chanson.
+narrateur|Nina se souvient de le tapis.
+narrateur|Elle se souvient de la chanson.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr"/>
@@ -6166,7 +6534,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a écouté sur le tapis. Elle a vécu la chanson. Le soir, elle a rejoint le doudou. Le doudou s'endort contre l'épaule. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6306,7 +6674,15 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a écouté sur le tapis.
+narrateur|Elle a vécu la chanson.
+narrateur|Le soir, elle a rejoint le doudou.
+narrateur|Le doudou s'endort contre l'épaule.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6334,7 +6710,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>À la table, Ninon écoute. Un mot la gêne. Malaise. Elle raconte à la maison.</t>
+          <t>Nina s'assoit à la table. Le bois a des lignes, tout fines. Un crayon jaune attend, tout lisse. On écoute, à la table. Nina écoute. Un mot la gêne, tout bas. C'est un chuchotement. Nina a un malaise. Ses mains deviennent chaudes. Elle pose le crayon, tout droit. Elle écoute la maîtresse, jusqu'au bout. Si tu as un malaise, tu racontes à la maison. Je raconte à papa. Ou à maman. Oui. D'abord, on écoute ici. Le crayon reste tiède, sous le doigt.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6470,7 +6846,23 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|À la table, Ninon écoute. Un mot la gêne. Malaise. Elle raconte à la maison.</t>
+          <t>narrateur|Nina s'assoit à la table.
+narrateur|Le bois a des lignes, tout fines.
+narrateur|Un crayon jaune attend, tout lisse.
+maitresse|On écoute, à la table.
+narrateur|Nina écoute.
+narrateur|Un mot la gêne, tout bas.
+narrateur|C'est un chuchotement.
+narrateur|Nina a un malaise.
+narrateur|Ses mains deviennent chaudes.
+narrateur|Elle pose le crayon, tout droit.
+narrateur|Elle écoute la maîtresse, jusqu'au bout.
+papa|Si tu as un malaise, tu racontes à la maison.
+enfant-f|Je raconte à papa.
+enfant-f|Ou à maman.
+maitresse|Oui.
+maitresse|D'abord, on écoute ici.
+narrateur|Le crayon reste tiède, sous le doigt.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr"/>
@@ -6498,7 +6890,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>À la table, Ninon a un malaise. Que fait-elle ?</t>
+          <t>À la table, Nina a un malaise. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6654,7 +7046,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|À la table, Ninon a un malaise. Que fait-elle ?</t>
+          <t>narrateur|À la table, Nina a un malaise.
+papa|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6682,7 +7075,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Écouter. Si malaise, raconter à la maison.</t>
+          <t>Oui. On écoute. Si malaise, on raconte à la maison. Nina essuie ses mains sur sa robe. Le tissu est un peu rêche. J'ai écouté. Et tu nous racontes. Bravo. Le crayon jaune reste sur la table.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6826,7 +7219,15 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Écouter. Si malaise, raconter à la maison.</t>
+          <t>papa|Oui.
+papa|On écoute.
+papa|Si malaise, on raconte à la maison.
+narrateur|Nina essuie ses mains sur sa robe.
+narrateur|Le tissu est un peu rêche.
+enfant-f|J'ai écouté.
+maman|Et tu nous racontes.
+maman|Bravo.
+narrateur|Le crayon jaune reste sur la table.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6854,7 +7255,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre l'histoire, le dessin, ou la chanson.</t>
+          <t>Trois choses encore, dans la classe. L'histoire, le dessin, ou la chanson ? On écoute. Ensuite, si malaise, on raconte à la maison.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7022,7 +7423,10 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre l'histoire, le dessin, ou la chanson.</t>
+          <t>narrateur|Trois choses encore, dans la classe.
+maitresse|L'histoire, le dessin, ou la chanson ?
+maman|On écoute.
+papa|Ensuite, si malaise, on raconte à la maison.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7050,7 +7454,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>À la table, l'histoire. Ninon écoute. Malaise. Raconter à la maison.</t>
+          <t>La maîtresse ouvre le livre. Il y a un renard, tout roux. Une page sent encore l'encre. On écoute l'histoire. Nina écoute. Le malaise est encore là, tout petit. Elle reste sage. Elle écoute jusqu'au bout. Je raconte à la maison. Oui. On t'écoute. Le livre est ouvert, au milieu de la table. Nina garde la table dans sa tête. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7190,7 +7594,21 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|À la table, l'histoire. Ninon écoute. Malaise. Raconter à la maison.</t>
+          <t>narrateur|La maîtresse ouvre le livre.
+narrateur|Il y a un renard, tout roux.
+narrateur|Une page sent encore l'encre.
+maitresse|On écoute l'histoire.
+narrateur|Nina écoute.
+narrateur|Le malaise est encore là, tout petit.
+narrateur|Elle reste sage.
+narrateur|Elle écoute jusqu'au bout.
+enfant-f|Je raconte à la maison.
+maman|Oui.
+maman|On t'écoute.
+narrateur|Le livre est ouvert, au milieu de la table.
+narrateur|Nina garde la table dans sa tête.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr"/>
@@ -7218,7 +7636,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre maman, papa, ou la sœur.</t>
+          <t>Le soir, à la maison, trois chemins. Maman, papa, ou le doudou ? On t'écoute.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7382,7 +7800,9 @@
       <c r="AV37" s="2" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+          <t>narrateur|Le soir, à la maison, trois chemins.
+maman|Maman, papa, ou le doudou ?
+papa|On t'écoute.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7410,7 +7830,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Ninon rejoint maman. Elle a écouté à la table, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
+          <t>Le soir, la cuisine sent la soupe. La louche fait un petit bruit, contre la casserole. Nina rejoint maman. Te voilà, Nina. Tu as faim ? Un peu. Nina pose le livre dans sa tête, près de l'assiette. Nina se souvient de la table. Elle se souvient de l'histoire. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7546,7 +7966,28 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Ninon rejoint maman. Elle a écouté à la table, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
+          <t>narrateur|Le soir, la cuisine sent la soupe.
+narrateur|La louche fait un petit bruit, contre la casserole.
+narrateur|Nina rejoint maman.
+maman|Te voilà, Nina.
+maman|Tu as faim ?
+enfant-f|Un peu.
+narrateur|Nina pose le livre dans sa tête, près de l'assiette.
+narrateur|Nina se souvient de la table.
+narrateur|Elle se souvient de l'histoire.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr"/>
@@ -7574,7 +8015,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a écouté à la table. Elle a vécu l'histoire. Le soir, elle a rejoint maman. La soupe fume encore, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7714,7 +8155,15 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a écouté à la table.
+narrateur|Elle a vécu l'histoire.
+narrateur|Le soir, elle a rejoint maman.
+narrateur|La soupe fume encore, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7742,7 +8191,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Ninon rejoint papa. Elle a écouté à la table, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
+          <t>Le soir, la lampe fait un rond jaune. Papa est dans le fauteuil. Nina rejoint papa. Viens. On a le temps. J'ai quelque chose. Papa écoute l'histoire de Nina, jusqu'au bout. Nina se souvient de la table. Elle se souvient de l'histoire. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7878,7 +8327,28 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Ninon rejoint papa. Elle a écouté à la table, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
+          <t>narrateur|Le soir, la lampe fait un rond jaune.
+narrateur|Papa est dans le fauteuil.
+narrateur|Nina rejoint papa.
+papa|Viens.
+papa|On a le temps.
+enfant-f|J'ai quelque chose.
+narrateur|Papa écoute l'histoire de Nina, jusqu'au bout.
+narrateur|Nina se souvient de la table.
+narrateur|Elle se souvient de l'histoire.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7906,7 +8376,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a écouté à la table. Elle a vécu l'histoire. Le soir, elle a rejoint papa. La lampe reste allumée, un moment. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8046,7 +8516,15 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a écouté à la table.
+narrateur|Elle a vécu l'histoire.
+narrateur|Le soir, elle a rejoint papa.
+narrateur|La lampe reste allumée, un moment.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8074,7 +8552,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Ninon rejoint la sœur. Elle a écouté à la table, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
+          <t>Le soir, le doudou attend sur le lit. Il est tiède, un peu froissé. Nina le serre. Toi d'abord. Puis elle va vers papa et maman. On t'écoute. Le doudou est sur la table de la cuisine, tout sage. Nina se souvient de la table. Elle se souvient de l'histoire. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8210,7 +8688,28 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Ninon rejoint la sœur. Elle a écouté à la table, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
+          <t>narrateur|Le soir, le doudou attend sur le lit.
+narrateur|Il est tiède, un peu froissé.
+narrateur|Nina le serre.
+enfant-f|Toi d'abord.
+narrateur|Puis elle va vers papa et maman.
+maman|On t'écoute.
+narrateur|Le doudou est sur la table de la cuisine, tout sage.
+narrateur|Nina se souvient de la table.
+narrateur|Elle se souvient de l'histoire.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr"/>
@@ -8238,7 +8737,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a écouté à la table. Elle a vécu l'histoire. Le soir, elle a rejoint le doudou. Le doudou s'endort contre l'épaule. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8378,7 +8877,15 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a écouté à la table.
+narrateur|Elle a vécu l'histoire.
+narrateur|Le soir, elle a rejoint le doudou.
+narrateur|Le doudou s'endort contre l'épaule.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8406,7 +8913,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Le dessin à la table. Ninon écoute. Malaise. Elle raconte à la maison.</t>
+          <t>Nina prend le crayon jaune. Le bois est lisse, un peu chaud. Elle dessine un rond, comme le soleil. On écoute, pendant le dessin. Nina écoute. Le malaise serre encore un peu. Elle pose le crayon, tout droit. Ce soir, je raconte. Tu as écouté. Ensuite, tu racontes. Le rond jaune brille sur le papier. Le crayon roule d'un doigt, sur la table. Nina garde la table dans sa tête. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8546,7 +9053,21 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Le dessin à la table. Ninon écoute. Malaise. Elle raconte à la maison.</t>
+          <t>narrateur|Nina prend le crayon jaune.
+narrateur|Le bois est lisse, un peu chaud.
+narrateur|Elle dessine un rond, comme le soleil.
+maitresse|On écoute, pendant le dessin.
+narrateur|Nina écoute.
+narrateur|Le malaise serre encore un peu.
+narrateur|Elle pose le crayon, tout droit.
+enfant-f|Ce soir, je raconte.
+papa|Tu as écouté.
+papa|Ensuite, tu racontes.
+narrateur|Le rond jaune brille sur le papier.
+narrateur|Le crayon roule d'un doigt, sur la table.
+narrateur|Nina garde la table dans sa tête.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr"/>
@@ -8574,7 +9095,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre maman, papa, ou la sœur.</t>
+          <t>Le soir, à la maison, trois chemins. Maman, papa, ou le doudou ? On t'écoute.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8738,7 +9259,9 @@
       <c r="AV45" s="2" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+          <t>narrateur|Le soir, à la maison, trois chemins.
+maman|Maman, papa, ou le doudou ?
+papa|On t'écoute.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8766,7 +9289,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Ninon rejoint maman. Elle a écouté à la table, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
+          <t>Le soir, la cuisine sent la soupe. La louche fait un petit bruit, contre la casserole. Nina rejoint maman. Te voilà, Nina. Tu as faim ? Un peu. Maman regarde le rond jaune, dans les mots de Nina. Nina se souvient de la table. Elle se souvient de le dessin. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8906,7 +9429,28 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Ninon rejoint maman. Elle a écouté à la table, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
+          <t>narrateur|Le soir, la cuisine sent la soupe.
+narrateur|La louche fait un petit bruit, contre la casserole.
+narrateur|Nina rejoint maman.
+maman|Te voilà, Nina.
+maman|Tu as faim ?
+enfant-f|Un peu.
+narrateur|Maman regarde le rond jaune, dans les mots de Nina.
+narrateur|Nina se souvient de la table.
+narrateur|Elle se souvient de le dessin.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr"/>
@@ -8934,7 +9478,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a écouté à la table. Elle a vécu le dessin. Le soir, elle a rejoint maman. La soupe fume encore, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9074,7 +9618,15 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a écouté à la table.
+narrateur|Elle a vécu le dessin.
+narrateur|Le soir, elle a rejoint maman.
+narrateur|La soupe fume encore, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9102,7 +9654,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Ninon rejoint papa. Elle a écouté à la table, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
+          <t>Le soir, la lampe fait un rond jaune. Papa est dans le fauteuil. Nina rejoint papa. Viens. On a le temps. J'ai quelque chose. Papa dit que le rond est beau, tout simple. Nina se souvient de la table. Elle se souvient de le dessin. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9242,7 +9794,28 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Ninon rejoint papa. Elle a écouté à la table, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
+          <t>narrateur|Le soir, la lampe fait un rond jaune.
+narrateur|Papa est dans le fauteuil.
+narrateur|Nina rejoint papa.
+papa|Viens.
+papa|On a le temps.
+enfant-f|J'ai quelque chose.
+narrateur|Papa dit que le rond est beau, tout simple.
+narrateur|Nina se souvient de la table.
+narrateur|Elle se souvient de le dessin.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9270,7 +9843,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a écouté à la table. Elle a vécu le dessin. Le soir, elle a rejoint papa. La lampe reste allumée, un moment. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9410,7 +9983,15 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a écouté à la table.
+narrateur|Elle a vécu le dessin.
+narrateur|Le soir, elle a rejoint papa.
+narrateur|La lampe reste allumée, un moment.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9438,7 +10019,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Ninon rejoint la sœur. Elle a écouté à la table, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
+          <t>Le soir, le doudou attend sur le lit. Il est tiède, un peu froissé. Nina le serre. Toi d'abord. Puis elle va vers papa et maman. On t'écoute. Le doudou tient le crayon, dans le récit de Nina. Nina se souvient de la table. Elle se souvient de le dessin. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9578,7 +10159,28 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Ninon rejoint la sœur. Elle a écouté à la table, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
+          <t>narrateur|Le soir, le doudou attend sur le lit.
+narrateur|Il est tiède, un peu froissé.
+narrateur|Nina le serre.
+enfant-f|Toi d'abord.
+narrateur|Puis elle va vers papa et maman.
+maman|On t'écoute.
+narrateur|Le doudou tient le crayon, dans le récit de Nina.
+narrateur|Nina se souvient de la table.
+narrateur|Elle se souvient de le dessin.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr"/>
@@ -9606,7 +10208,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a écouté à la table. Elle a vécu le dessin. Le soir, elle a rejoint le doudou. Le doudou s'endort contre l'épaule. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9746,7 +10348,15 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a écouté à la table.
+narrateur|Elle a vécu le dessin.
+narrateur|Le soir, elle a rejoint le doudou.
+narrateur|Le doudou s'endort contre l'épaule.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9774,7 +10384,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>La chanson à la table. Ninon écoute. Malaise. Raconter à la maison.</t>
+          <t>La maîtresse tape deux fois dans les mains. La chanson est douce, tout simple. On écoute la chanson. Nina écoute. Elle ne chuchote pas. Le malaise reste, tout petit. Je raconte à maman. Ou à papa. Oui. Si malaise, tu racontes à la maison. Les mains de Nina se posent sur ses genoux. La table vibre un peu, avec la chanson. Nina garde la table dans sa tête. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9914,10 +10524,28 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|La chanson à la table. Ninon écoute. Malaise. Raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr"/>
+          <t>narrateur|La maîtresse tape deux fois dans les mains.
+narrateur|La chanson est douce, tout simple.
+maitresse|On écoute la chanson.
+narrateur|Nina écoute.
+narrateur|Elle ne chuchote pas.
+narrateur|Le malaise reste, tout petit.
+enfant-f|Je raconte à maman.
+enfant-f|Ou à papa.
+maman|Oui.
+maman|Si malaise, tu racontes à la maison.
+narrateur|Les mains de Nina se posent sur ses genoux.
+narrateur|La table vibre un peu, avec la chanson.
+narrateur|Nina garde la table dans sa tête.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>chanson</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9942,7 +10570,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre maman, papa, ou la sœur.</t>
+          <t>Le soir, à la maison, trois chemins. Maman, papa, ou le doudou ? On t'écoute.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10106,7 +10734,9 @@
       <c r="AV53" s="2" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+          <t>narrateur|Le soir, à la maison, trois chemins.
+maman|Maman, papa, ou le doudou ?
+papa|On t'écoute.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10134,7 +10764,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Ninon rejoint maman. Elle a écouté à la table, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
+          <t>Le soir, la cuisine sent la soupe. La louche fait un petit bruit, contre la casserole. Nina rejoint maman. Te voilà, Nina. Tu as faim ? Un peu. Maman tapote la casserole, comme la chanson. Nina se souvient de la table. Elle se souvient de la chanson. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10270,7 +10900,28 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Ninon rejoint maman. Elle a écouté à la table, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
+          <t>narrateur|Le soir, la cuisine sent la soupe.
+narrateur|La louche fait un petit bruit, contre la casserole.
+narrateur|Nina rejoint maman.
+maman|Te voilà, Nina.
+maman|Tu as faim ?
+enfant-f|Un peu.
+narrateur|Maman tapote la casserole, comme la chanson.
+narrateur|Nina se souvient de la table.
+narrateur|Elle se souvient de la chanson.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr"/>
@@ -10298,7 +10949,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a écouté à la table. Elle a vécu la chanson. Le soir, elle a rejoint maman. La soupe fume encore, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10438,7 +11089,15 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a écouté à la table.
+narrateur|Elle a vécu la chanson.
+narrateur|Le soir, elle a rejoint maman.
+narrateur|La soupe fume encore, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10466,7 +11125,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Ninon rejoint papa. Elle a écouté à la table, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
+          <t>Le soir, la lampe fait un rond jaune. Papa est dans le fauteuil. Nina rejoint papa. Viens. On a le temps. J'ai quelque chose. Papa tapote le fauteuil, tout doux. Nina se souvient de la table. Elle se souvient de la chanson. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10602,7 +11261,28 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Ninon rejoint papa. Elle a écouté à la table, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
+          <t>narrateur|Le soir, la lampe fait un rond jaune.
+narrateur|Papa est dans le fauteuil.
+narrateur|Nina rejoint papa.
+papa|Viens.
+papa|On a le temps.
+enfant-f|J'ai quelque chose.
+narrateur|Papa tapote le fauteuil, tout doux.
+narrateur|Nina se souvient de la table.
+narrateur|Elle se souvient de la chanson.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10630,7 +11310,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a écouté à la table. Elle a vécu la chanson. Le soir, elle a rejoint papa. La lampe reste allumée, un moment. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10770,7 +11450,15 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a écouté à la table.
+narrateur|Elle a vécu la chanson.
+narrateur|Le soir, elle a rejoint papa.
+narrateur|La lampe reste allumée, un moment.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10798,7 +11486,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Ninon rejoint la sœur. Elle a écouté à la table, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
+          <t>Le soir, le doudou attend sur le lit. Il est tiède, un peu froissé. Nina le serre. Toi d'abord. Puis elle va vers papa et maman. On t'écoute. Le doudou a entendu la chanson, tout près. Nina se souvient de la table. Elle se souvient de la chanson. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -10934,7 +11622,28 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Ninon rejoint la sœur. Elle a écouté à la table, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
+          <t>narrateur|Le soir, le doudou attend sur le lit.
+narrateur|Il est tiède, un peu froissé.
+narrateur|Nina le serre.
+enfant-f|Toi d'abord.
+narrateur|Puis elle va vers papa et maman.
+maman|On t'écoute.
+narrateur|Le doudou a entendu la chanson, tout près.
+narrateur|Nina se souvient de la table.
+narrateur|Elle se souvient de la chanson.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr"/>
@@ -10962,7 +11671,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a écouté à la table. Elle a vécu la chanson. Le soir, elle a rejoint le doudou. Le doudou s'endort contre l'épaule. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11102,7 +11811,15 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a écouté à la table.
+narrateur|Elle a vécu la chanson.
+narrateur|Le soir, elle a rejoint le doudou.
+narrateur|Le doudou s'endort contre l'épaule.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11130,7 +11847,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Au préau, Ninon écoute. Son ventre se serre. Malaise. Elle racontera à la maison.</t>
+          <t>Nina va au préau. Les carreaux sont froids, un peu humides. Une goutte tombe du toit, tout loin. On écoute, au préau. Nina écoute. Un camarade parle tout bas. Le ventre de Nina se serre. Elle respire. Elle reste près de la maîtresse. Papa t'écoute, à la maison. Moi aussi. Ce soir, je raconte. Tu as bien écouté. La goutte fait encore un ploc, tout petit. Nina garde les mains dans ses poches.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11270,10 +11987,28 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Au préau, Ninon écoute. Son ventre se serre. Malaise. Elle racontera à la maison.</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr"/>
+          <t>narrateur|Nina va au préau.
+narrateur|Les carreaux sont froids, un peu humides.
+narrateur|Une goutte tombe du toit, tout loin.
+maitresse|On écoute, au préau.
+narrateur|Nina écoute.
+narrateur|Un camarade parle tout bas.
+narrateur|Le ventre de Nina se serre.
+narrateur|Elle respire.
+narrateur|Elle reste près de la maîtresse.
+maman|Papa t'écoute, à la maison.
+maman|Moi aussi.
+enfant-f|Ce soir, je raconte.
+maitresse|Tu as bien écouté.
+narrateur|La goutte fait encore un ploc, tout petit.
+narrateur|Nina garde les mains dans ses poches.</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>goutte</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11298,7 +12033,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Au préau, Ninon a un malaise. Que fait-elle ?</t>
+          <t>Au préau, Nina a un malaise. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11454,7 +12189,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Au préau, Ninon a un malaise. Que fait-elle ?</t>
+          <t>narrateur|Au préau, Nina a un malaise.
+maman|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11482,7 +12218,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Ninon a su écouter. Elle saura raconter à la maison.</t>
+          <t>Oui. Nina a écouté. Elle raconte à la maison. Nina lève les yeux. Le toit du préau est gris, tout calme. Je raconte ce soir. On t'écoute. Bravo, Nina. La goutte s'est arrêtée.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11626,7 +12362,15 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Ninon a su écouter. Elle saura raconter à la maison.</t>
+          <t>maman|Oui.
+maman|Nina a écouté.
+maman|Elle raconte à la maison.
+narrateur|Nina lève les yeux.
+narrateur|Le toit du préau est gris, tout calme.
+enfant-f|Je raconte ce soir.
+papa|On t'écoute.
+papa|Bravo, Nina.
+narrateur|La goutte s'est arrêtée.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11654,7 +12398,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre l'histoire, le dessin, ou la chanson.</t>
+          <t>Trois choses encore, dans la classe. L'histoire, le dessin, ou la chanson ? On écoute. Ensuite, si malaise, on raconte à la maison.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11822,7 +12566,10 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre l'histoire, le dessin, ou la chanson.</t>
+          <t>narrateur|Trois choses encore, dans la classe.
+maitresse|L'histoire, le dessin, ou la chanson ?
+maman|On écoute.
+papa|Ensuite, si malaise, on raconte à la maison.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11850,7 +12597,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Au préau, l'histoire. Ninon écoute. Malaise. Elle raconte à la maison.</t>
+          <t>La maîtresse ouvre le livre. Il y a un renard, tout roux. Une page sent encore l'encre. On écoute l'histoire. Nina écoute. Le malaise est encore là, tout petit. Elle reste sage. Elle écoute jusqu'au bout. Je raconte à la maison. Oui. On t'écoute. Le vent tourne une page, au préau. Nina garde le préau dans sa tête. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -11986,7 +12733,21 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Au préau, l'histoire. Ninon écoute. Malaise. Elle raconte à la maison.</t>
+          <t>narrateur|La maîtresse ouvre le livre.
+narrateur|Il y a un renard, tout roux.
+narrateur|Une page sent encore l'encre.
+maitresse|On écoute l'histoire.
+narrateur|Nina écoute.
+narrateur|Le malaise est encore là, tout petit.
+narrateur|Elle reste sage.
+narrateur|Elle écoute jusqu'au bout.
+enfant-f|Je raconte à la maison.
+maman|Oui.
+maman|On t'écoute.
+narrateur|Le vent tourne une page, au préau.
+narrateur|Nina garde le préau dans sa tête.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr"/>
@@ -12014,7 +12775,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre maman, papa, ou la sœur.</t>
+          <t>Le soir, à la maison, trois chemins. Maman, papa, ou le doudou ? On t'écoute.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12178,7 +12939,9 @@
       <c r="AV65" s="2" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+          <t>narrateur|Le soir, à la maison, trois chemins.
+maman|Maman, papa, ou le doudou ?
+papa|On t'écoute.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12206,7 +12969,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Ninon rejoint maman. Elle a écouté à le préau, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
+          <t>Le soir, la cuisine sent la soupe. La louche fait un petit bruit, contre la casserole. Nina rejoint maman. Te voilà, Nina. Tu as faim ? Un peu. Nina raconte le préau, et le renard du livre. Nina se souvient de le préau. Elle se souvient de l'histoire. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12342,7 +13105,28 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Ninon rejoint maman. Elle a écouté à le préau, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
+          <t>narrateur|Le soir, la cuisine sent la soupe.
+narrateur|La louche fait un petit bruit, contre la casserole.
+narrateur|Nina rejoint maman.
+maman|Te voilà, Nina.
+maman|Tu as faim ?
+enfant-f|Un peu.
+narrateur|Nina raconte le préau, et le renard du livre.
+narrateur|Nina se souvient de le préau.
+narrateur|Elle se souvient de l'histoire.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr"/>
@@ -12370,7 +13154,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a écouté au préau. Elle a vécu l'histoire. Le soir, elle a rejoint maman. La soupe fume encore, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12510,7 +13294,15 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a écouté au préau.
+narrateur|Elle a vécu l'histoire.
+narrateur|Le soir, elle a rejoint maman.
+narrateur|La soupe fume encore, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12538,7 +13330,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Ninon rejoint papa. Elle a écouté à le préau, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
+          <t>Le soir, la lampe fait un rond jaune. Papa est dans le fauteuil. Nina rejoint papa. Viens. On a le temps. J'ai quelque chose. Papa entend encore le ploc, dans l'histoire. Nina se souvient de le préau. Elle se souvient de l'histoire. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12674,7 +13466,28 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Ninon rejoint papa. Elle a écouté à le préau, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
+          <t>narrateur|Le soir, la lampe fait un rond jaune.
+narrateur|Papa est dans le fauteuil.
+narrateur|Nina rejoint papa.
+papa|Viens.
+papa|On a le temps.
+enfant-f|J'ai quelque chose.
+narrateur|Papa entend encore le ploc, dans l'histoire.
+narrateur|Nina se souvient de le préau.
+narrateur|Elle se souvient de l'histoire.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12702,7 +13515,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a écouté au préau. Elle a vécu l'histoire. Le soir, elle a rejoint papa. La lampe reste allumée, un moment. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12842,7 +13655,15 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a écouté au préau.
+narrateur|Elle a vécu l'histoire.
+narrateur|Le soir, elle a rejoint papa.
+narrateur|La lampe reste allumée, un moment.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12870,7 +13691,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Ninon rejoint la sœur. Elle a écouté à le préau, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
+          <t>Le soir, le doudou attend sur le lit. Il est tiède, un peu froissé. Nina le serre. Toi d'abord. Puis elle va vers papa et maman. On t'écoute. Le doudou a une goutte imaginaire, sur le nez. Nina se souvient de le préau. Elle se souvient de l'histoire. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13006,7 +13827,28 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Ninon rejoint la sœur. Elle a écouté à le préau, pendant l'histoire. Un malaise. Elle raconte à la maison.</t>
+          <t>narrateur|Le soir, le doudou attend sur le lit.
+narrateur|Il est tiède, un peu froissé.
+narrateur|Nina le serre.
+enfant-f|Toi d'abord.
+narrateur|Puis elle va vers papa et maman.
+maman|On t'écoute.
+narrateur|Le doudou a une goutte imaginaire, sur le nez.
+narrateur|Nina se souvient de le préau.
+narrateur|Elle se souvient de l'histoire.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr"/>
@@ -13034,7 +13876,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a écouté au préau. Elle a vécu l'histoire. Le soir, elle a rejoint le doudou. Le doudou s'endort contre l'épaule. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13174,7 +14016,15 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a écouté au préau.
+narrateur|Elle a vécu l'histoire.
+narrateur|Le soir, elle a rejoint le doudou.
+narrateur|Le doudou s'endort contre l'épaule.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13202,7 +14052,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Le dessin au préau. Ninon écoute. Malaise. Raconter à la maison.</t>
+          <t>Nina prend le crayon jaune. Le bois est lisse, un peu chaud. Elle dessine un rond, comme le soleil. On écoute, pendant le dessin. Nina écoute. Le malaise serre encore un peu. Elle pose le crayon, tout droit. Ce soir, je raconte. Tu as écouté. Ensuite, tu racontes. Le rond jaune brille sur le papier. Le papier claque un peu, au préau. Nina garde le préau dans sa tête. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13342,7 +14192,21 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Le dessin au préau. Ninon écoute. Malaise. Raconter à la maison.</t>
+          <t>narrateur|Nina prend le crayon jaune.
+narrateur|Le bois est lisse, un peu chaud.
+narrateur|Elle dessine un rond, comme le soleil.
+maitresse|On écoute, pendant le dessin.
+narrateur|Nina écoute.
+narrateur|Le malaise serre encore un peu.
+narrateur|Elle pose le crayon, tout droit.
+enfant-f|Ce soir, je raconte.
+papa|Tu as écouté.
+papa|Ensuite, tu racontes.
+narrateur|Le rond jaune brille sur le papier.
+narrateur|Le papier claque un peu, au préau.
+narrateur|Nina garde le préau dans sa tête.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr"/>
@@ -13370,7 +14234,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre maman, papa, ou la sœur.</t>
+          <t>Le soir, à la maison, trois chemins. Maman, papa, ou le doudou ? On t'écoute.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13534,7 +14398,9 @@
       <c r="AV73" s="2" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+          <t>narrateur|Le soir, à la maison, trois chemins.
+maman|Maman, papa, ou le doudou ?
+papa|On t'écoute.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13562,7 +14428,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Ninon rejoint maman. Elle a écouté à le préau, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
+          <t>Le soir, la cuisine sent la soupe. La louche fait un petit bruit, contre la casserole. Nina rejoint maman. Te voilà, Nina. Tu as faim ? Un peu. Nina dessine le préau, avec des mots. Nina se souvient de le préau. Elle se souvient de le dessin. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13702,7 +14568,28 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Ninon rejoint maman. Elle a écouté à le préau, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
+          <t>narrateur|Le soir, la cuisine sent la soupe.
+narrateur|La louche fait un petit bruit, contre la casserole.
+narrateur|Nina rejoint maman.
+maman|Te voilà, Nina.
+maman|Tu as faim ?
+enfant-f|Un peu.
+narrateur|Nina dessine le préau, avec des mots.
+narrateur|Nina se souvient de le préau.
+narrateur|Elle se souvient de le dessin.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr"/>
@@ -13730,7 +14617,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a écouté au préau. Elle a vécu le dessin. Le soir, elle a rejoint maman. La soupe fume encore, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13870,7 +14757,15 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a écouté au préau.
+narrateur|Elle a vécu le dessin.
+narrateur|Le soir, elle a rejoint maman.
+narrateur|La soupe fume encore, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -13898,7 +14793,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Ninon rejoint papa. Elle a écouté à le préau, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
+          <t>Le soir, la lampe fait un rond jaune. Papa est dans le fauteuil. Nina rejoint papa. Viens. On a le temps. J'ai quelque chose. Papa voit le toit gris, dans le dessin raconté. Nina se souvient de le préau. Elle se souvient de le dessin. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14038,7 +14933,28 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Ninon rejoint papa. Elle a écouté à le préau, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
+          <t>narrateur|Le soir, la lampe fait un rond jaune.
+narrateur|Papa est dans le fauteuil.
+narrateur|Nina rejoint papa.
+papa|Viens.
+papa|On a le temps.
+enfant-f|J'ai quelque chose.
+narrateur|Papa voit le toit gris, dans le dessin raconté.
+narrateur|Nina se souvient de le préau.
+narrateur|Elle se souvient de le dessin.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14066,7 +14982,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a écouté au préau. Elle a vécu le dessin. Le soir, elle a rejoint papa. La lampe reste allumée, un moment. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14206,7 +15122,15 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a écouté au préau.
+narrateur|Elle a vécu le dessin.
+narrateur|Le soir, elle a rejoint papa.
+narrateur|La lampe reste allumée, un moment.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14234,7 +15158,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Ninon rejoint la sœur. Elle a écouté à le préau, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
+          <t>Le soir, le doudou attend sur le lit. Il est tiède, un peu froissé. Nina le serre. Toi d'abord. Puis elle va vers papa et maman. On t'écoute. Le doudou a froid, comme les carreaux du préau. Nina se souvient de le préau. Elle se souvient de le dessin. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14374,7 +15298,28 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Ninon rejoint la sœur. Elle a écouté à le préau, pendant le dessin. Un malaise. Elle raconte à la maison.</t>
+          <t>narrateur|Le soir, le doudou attend sur le lit.
+narrateur|Il est tiède, un peu froissé.
+narrateur|Nina le serre.
+enfant-f|Toi d'abord.
+narrateur|Puis elle va vers papa et maman.
+maman|On t'écoute.
+narrateur|Le doudou a froid, comme les carreaux du préau.
+narrateur|Nina se souvient de le préau.
+narrateur|Elle se souvient de le dessin.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr"/>
@@ -14402,7 +15347,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a écouté au préau. Elle a vécu le dessin. Le soir, elle a rejoint le doudou. Le doudou s'endort contre l'épaule. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14542,7 +15487,15 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a écouté au préau.
+narrateur|Elle a vécu le dessin.
+narrateur|Le soir, elle a rejoint le doudou.
+narrateur|Le doudou s'endort contre l'épaule.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14570,7 +15523,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>La chanson au préau. Ninon écoute. Malaise. Elle raconte à la maison.</t>
+          <t>La maîtresse tape deux fois dans les mains. La chanson est douce, tout simple. On écoute la chanson. Nina écoute. Elle ne chuchote pas. Le malaise reste, tout petit. Je raconte à maman. Ou à papa. Oui. Si malaise, tu racontes à la maison. Les mains de Nina se posent sur ses genoux. La chanson revient en écho, sous le toit. Nina garde le préau dans sa tête. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14706,10 +15659,28 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|La chanson au préau. Ninon écoute. Malaise. Elle raconte à la maison.</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr"/>
+          <t>narrateur|La maîtresse tape deux fois dans les mains.
+narrateur|La chanson est douce, tout simple.
+maitresse|On écoute la chanson.
+narrateur|Nina écoute.
+narrateur|Elle ne chuchote pas.
+narrateur|Le malaise reste, tout petit.
+enfant-f|Je raconte à maman.
+enfant-f|Ou à papa.
+maman|Oui.
+maman|Si malaise, tu racontes à la maison.
+narrateur|Les mains de Nina se posent sur ses genoux.
+narrateur|La chanson revient en écho, sous le toit.
+narrateur|Nina garde le préau dans sa tête.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>chanson</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14734,7 +15705,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre maman, papa, ou la sœur.</t>
+          <t>Le soir, à la maison, trois chemins. Maman, papa, ou le doudou ? On t'écoute.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -14898,7 +15869,9 @@
       <c r="AV81" s="2" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+          <t>narrateur|Le soir, à la maison, trois chemins.
+maman|Maman, papa, ou le doudou ?
+papa|On t'écoute.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -14926,7 +15899,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Ninon rejoint maman. Elle a écouté à le préau, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
+          <t>Le soir, la cuisine sent la soupe. La louche fait un petit bruit, contre la casserole. Nina rejoint maman. Te voilà, Nina. Tu as faim ? Un peu. La chanson du préau revient, près de la soupe. Nina se souvient de le préau. Elle se souvient de la chanson. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15062,7 +16035,28 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Ninon rejoint maman. Elle a écouté à le préau, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
+          <t>narrateur|Le soir, la cuisine sent la soupe.
+narrateur|La louche fait un petit bruit, contre la casserole.
+narrateur|Nina rejoint maman.
+maman|Te voilà, Nina.
+maman|Tu as faim ?
+enfant-f|Un peu.
+narrateur|La chanson du préau revient, près de la soupe.
+narrateur|Nina se souvient de le préau.
+narrateur|Elle se souvient de la chanson.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr"/>
@@ -15090,7 +16084,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a écouté au préau. Elle a vécu la chanson. Le soir, elle a rejoint maman. La soupe fume encore, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15230,7 +16224,15 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a écouté au préau.
+narrateur|Elle a vécu la chanson.
+narrateur|Le soir, elle a rejoint maman.
+narrateur|La soupe fume encore, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15258,7 +16260,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Ninon rejoint papa. Elle a écouté à le préau, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
+          <t>Le soir, la lampe fait un rond jaune. Papa est dans le fauteuil. Nina rejoint papa. Viens. On a le temps. J'ai quelque chose. Papa écoute l'écho, dans la voix de Nina. Nina se souvient de le préau. Elle se souvient de la chanson. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15394,7 +16396,28 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Ninon rejoint papa. Elle a écouté à le préau, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
+          <t>narrateur|Le soir, la lampe fait un rond jaune.
+narrateur|Papa est dans le fauteuil.
+narrateur|Nina rejoint papa.
+papa|Viens.
+papa|On a le temps.
+enfant-f|J'ai quelque chose.
+narrateur|Papa écoute l'écho, dans la voix de Nina.
+narrateur|Nina se souvient de le préau.
+narrateur|Elle se souvient de la chanson.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15422,7 +16445,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a écouté au préau. Elle a vécu la chanson. Le soir, elle a rejoint papa. La lampe reste allumée, un moment. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15562,7 +16585,15 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a écouté au préau.
+narrateur|Elle a vécu la chanson.
+narrateur|Le soir, elle a rejoint papa.
+narrateur|La lampe reste allumée, un moment.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15590,7 +16621,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Ninon rejoint la sœur. Elle a écouté à le préau, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
+          <t>Le soir, le doudou attend sur le lit. Il est tiède, un peu froissé. Nina le serre. Toi d'abord. Puis elle va vers papa et maman. On t'écoute. Le doudou connaît le rythme, tout petit. Nina se souvient de le préau. Elle se souvient de la chanson. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15726,7 +16757,28 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Ninon rejoint la sœur. Elle a écouté à le préau, pendant la chanson. Un malaise. Elle raconte à la maison.</t>
+          <t>narrateur|Le soir, le doudou attend sur le lit.
+narrateur|Il est tiède, un peu froissé.
+narrateur|Nina le serre.
+enfant-f|Toi d'abord.
+narrateur|Puis elle va vers papa et maman.
+maman|On t'écoute.
+narrateur|Le doudou connaît le rythme, tout petit.
+narrateur|Nina se souvient de le préau.
+narrateur|Elle se souvient de la chanson.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr"/>
@@ -15754,7 +16806,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a écouté au préau. Elle a vécu la chanson. Le soir, elle a rejoint le doudou. Le doudou s'endort contre l'épaule. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -15894,7 +16946,15 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a écouté au préau.
+narrateur|Elle a vécu la chanson.
+narrateur|Le soir, elle a rejoint le doudou.
+narrateur|Le doudou s'endort contre l'épaule.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -15916,7 +16976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15954,6 +17014,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>
